--- a/project/CLEAN_DATASETS/issues_log.xlsx
+++ b/project/CLEAN_DATASETS/issues_log.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vfrancisco\Desktop\repos\gacelapay_fraud_analysis\project\CLEAN_DATASETS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C056F7-6FB8-4C31-9BB0-63D04E5F7057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BFEF4-92F5-4272-8F7B-01BAA7C5E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{46F2C2DC-CD36-48EA-89A3-B17E2329398E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46F2C2DC-CD36-48EA-89A3-B17E2329398E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ACCOUNTS" sheetId="1" r:id="rId1"/>
+    <sheet name="CURRENCY_EXCHANGE_RATES" sheetId="2" r:id="rId1"/>
+    <sheet name="ACCOUNTS" sheetId="1" r:id="rId2"/>
+    <sheet name="CUSTOMERS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
   <si>
     <t>COLUMN</t>
   </si>
@@ -81,9 +83,6 @@
   </si>
   <si>
     <t>TYPE</t>
-  </si>
-  <si>
-    <t>Leading and trailing spaces. There are 5 different types, but they are inconsistent, sometimes it comes uppercase, just the initial capitalized, or lowercase. Also has unisable values used to filter the rows. Already explained on the ID issue</t>
   </si>
   <si>
     <t>CURRENCY</t>
@@ -128,12 +127,115 @@
   <si>
     <t>Used TRIM and CASE to match and resolve the issues only outputting the uppercase version of the status.</t>
   </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>There are 5 main currencies that we manage, giving 10 possible exchange rate combinations, each in its own file. The files only have 2 columns, one for data and the other with the opening rate for that day. The headers are unclean and their names need to be changed. All these 10 files should be condensed into a single table for better handling.</t>
+  </si>
+  <si>
+    <t>Used JOIN to merge all these files into 1 table, changed the column names and filtered the wrong headers that appeared.</t>
+  </si>
+  <si>
+    <t>FIRST_NAME</t>
+  </si>
+  <si>
+    <t>LAST_NAME</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>CREDIT_LIMIT</t>
+  </si>
+  <si>
+    <t>CUSTOMER_LIFETIME_VALUE</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Inconsistent Format. Sometimes shows full english country name, or the alpha-2 country code, uppercase and lowercase.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used the python library </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"gender_guesser" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to assume the gender based on customer's name only when the gender was missing. library does not connect to the internet to guess the name, so, no risk of exposing sensible customer information. There were 2 names that could not be detected, so hardcoded its gender manually in the code. Finally returned the gender in uppercase.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used the python library </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"pycountry" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to get the full english country name when only 2 characters were present. Returned the uppercase full country name.</t>
+    </r>
+  </si>
+  <si>
+    <t>Missing genders.</t>
+  </si>
+  <si>
+    <t>Wrapped in single and double cuotes.</t>
+  </si>
+  <si>
+    <t>Leading and trailing spaces. There are 5 different types, but they are inconsistent, sometimes it comes uppercase, just the initial capitalized, or lowercase. Also has unisable values used to filter the rows. Already explained on the ID issue.</t>
+  </si>
+  <si>
+    <t>All numbers begin with the $ symbol, shows the comma format of the number and trailing spaces.</t>
+  </si>
+  <si>
+    <t>Comma format and number is wrapped around single quotes</t>
+  </si>
+  <si>
+    <t>Used REPLACE to get rid of those characters.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +244,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -275,7 +385,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="30">
     <dxf>
       <font>
         <strike val="0"/>
@@ -301,46 +411,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -485,6 +555,468 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -501,14 +1033,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}" name="Table1" displayName="Table1" ref="A1:E9" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05C0FE4D-3D83-48C0-8912-23AD1347B2CD}" name="CURRENCY_EXCHANGE_RATES_LOG" displayName="CURRENCY_EXCHANGE_RATES_LOG" ref="A1:E2" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+  <autoFilter ref="A1:E2" xr:uid="{05C0FE4D-3D83-48C0-8912-23AD1347B2CD}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2E40A0B3-AF90-4182-9843-2288801456DE}" name="COLUMN" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{F80B9787-EB7F-4E48-848A-5C6AA8F617DA}" name="ISSUE" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{0AB4CDCB-C236-4A3C-A4A4-9D44F21813D8}" name="ROW_COUNT" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{54E6A82B-991C-4065-96DF-727003752F56}" name="SOLVABLE?" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{7862C159-CC1E-4693-A947-D23804304F60}" name="RESOLUTION" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}" name="ACCOUNTS_LOG" displayName="ACCOUNTS_LOG" ref="A1:E9" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:E9" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24C76CF5-60AC-4D99-B257-103FA77CA877}" name="COLUMN" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3337A670-71E0-4223-B5A5-44BCF535FADF}" name="ISSUE" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{75E5D8EA-C827-466C-A54E-C6D233FF37A9}" name="ROW_COUNT" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{E754BFA5-49D4-4DE6-974C-68E66960C0FB}" name="SOLVABLE?" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{E655503B-E1BA-4C6B-855C-199DC3D0C0C1}" name="RESOLUTION" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{24C76CF5-60AC-4D99-B257-103FA77CA877}" name="COLUMN" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{3337A670-71E0-4223-B5A5-44BCF535FADF}" name="ISSUE" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{75E5D8EA-C827-466C-A54E-C6D233FF37A9}" name="ROW_COUNT" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{E754BFA5-49D4-4DE6-974C-68E66960C0FB}" name="SOLVABLE?" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E655503B-E1BA-4C6B-855C-199DC3D0C0C1}" name="RESOLUTION" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80E774B3-ED81-44B3-B55B-CB30FBB2CC6A}" name="CUSTOMERS_LOG" displayName="CUSTOMERS_LOG" ref="A1:E7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E7" xr:uid="{80E774B3-ED81-44B3-B55B-CB30FBB2CC6A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{61E96C8D-2220-4567-BB54-92EC049CF4F5}" name="COLUMN" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D071CD65-CD39-4278-9D0A-DFB78B630E35}" name="ISSUE" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{83A03F84-5429-40D2-9146-4D040C3B0952}" name="ROW_COUNT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{9E8CE933-1F0D-4B77-B634-8E01CE3B889D}" name="SOLVABLE?" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{FA4FB0EF-2A46-4B38-9DA8-CA7E9F384D25}" name="RESOLUTION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -830,6 +1390,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B000EDFD-1BFB-42C1-BFFA-C3C04EB2B5BC}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="147" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AA644F-2F2F-4C85-9D29-B7B920A959A3}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.25"/>
@@ -915,7 +1529,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>6</v>
@@ -924,15 +1538,15 @@
         <v>8</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="126" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>6</v>
@@ -941,15 +1555,15 @@
         <v>8</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="63" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>6</v>
@@ -958,15 +1572,15 @@
         <v>8</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="399" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>6</v>
@@ -975,15 +1589,15 @@
         <v>8</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="84" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>6</v>
@@ -992,7 +1606,146 @@
         <v>8</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE24E73-34C4-4132-9833-420D4EADE018}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="99.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="7">
+        <v>483</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="84" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="42" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/project/CLEAN_DATASETS/issues_log.xlsx
+++ b/project/CLEAN_DATASETS/issues_log.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vfrancisco\Desktop\repos\gacelapay_fraud_analysis\project\CLEAN_DATASETS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BFEF4-92F5-4272-8F7B-01BAA7C5E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8042A5-9142-45DC-8D49-D05C684AA335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46F2C2DC-CD36-48EA-89A3-B17E2329398E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{46F2C2DC-CD36-48EA-89A3-B17E2329398E}"/>
   </bookViews>
   <sheets>
     <sheet name="CURRENCY_EXCHANGE_RATES" sheetId="2" r:id="rId1"/>
     <sheet name="ACCOUNTS" sheetId="1" r:id="rId2"/>
     <sheet name="CUSTOMERS" sheetId="3" r:id="rId3"/>
+    <sheet name="FRAUD_DECISIONS" sheetId="4" r:id="rId4"/>
+    <sheet name="TRANSACTIONS" sheetId="5" r:id="rId5"/>
+    <sheet name="FRAUD_COSTS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
   <si>
     <t>COLUMN</t>
   </si>
@@ -229,6 +232,90 @@
   </si>
   <si>
     <t>Used REPLACE to get rid of those characters.</t>
+  </si>
+  <si>
+    <t>Not an issue, but column is unnecessary for analysis, since it maintains a 1-1 relationship the the main fact table TRANSACTIONS.</t>
+  </si>
+  <si>
+    <t>Not included in clean dataset.</t>
+  </si>
+  <si>
+    <t>ML_SCORE</t>
+  </si>
+  <si>
+    <t>Scores are coming wrapped in double quotes</t>
+  </si>
+  <si>
+    <t>Used REPLACE to get rid of unwanted characters.</t>
+  </si>
+  <si>
+    <t>DECISION_TIME</t>
+  </si>
+  <si>
+    <t>Null values</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>This column is unusable since more than 50% of values are missing.</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Column is coming in integer format. Probaby 1900 format from Excel. Time is also inside this value in decimal format. Would be cleaner to separate these values.</t>
+  </si>
+  <si>
+    <t>Column separated into DATE and TIME.
+DATE: Converted to date format calculating the current day by adding the floor number from the TIMESTAMP column (the number without the decimal part) to the date 1899-12-31, and substracting 1, since There is a known Excel bug which records the year 1900 as a leap year, hence counting the incorrect date 1900-02-29. This date was removed by substracting 1.
+TIME: Since the decimal part is a proportion of the seconds in a day, obtained the time column by first getting how many seconds there where for that time, multipling the module of TIMESTAMP % 1 to get decimal part, by 86,400 (quantity of seconds in a day) and used ROUND to get an integer rounded value to represent the quantity of seconds. Then the seconds were converted into time by adding to the time 00:00:00 (12 AM in the morning).</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>It is storing both the amount and the currency as text.</t>
+  </si>
+  <si>
+    <t>Column separated into AMOUNT and CURRENCY. Used SPLIT_PART and separeted by space to get both values in 2 columns.</t>
+  </si>
+  <si>
+    <t>ACCOUNT_FEES</t>
+  </si>
+  <si>
+    <t>Account fees are calculated for every transaction, regardless whether it was blocked or not by the ML model. Blocked transactions do not yield interest since they are not settled.</t>
+  </si>
+  <si>
+    <t>Joined with the cleaned table FRAUD_DECISIONS to determine if transactions where blocked or not. If blocked, then return a 0 for that transaction.</t>
+  </si>
+  <si>
+    <t>MERCHANT_CATEGORY</t>
+  </si>
+  <si>
+    <t>The names are lowecase and separated by underscore. Inconsistent naming for values "web", "web-browser" and "web_payment".</t>
+  </si>
+  <si>
+    <t>Replaced underscores with spaces. Returned Uppercase text. Joined the categories "web", "web-browser" and "web_payment" as just "WEB".</t>
+  </si>
+  <si>
+    <t>Inconsistent values for boolean results. Sometimes return as number, or text in inconsistent way.</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Replaced "Y" and "TRUE" with 1, since these values represent affirmation. Yes and true.
+Replaced "N" and "FALSE" with 0, since these values represent negation. No and false.</t>
+  </si>
+  <si>
+    <t>INVESTIGATION_COST, CUSTOMER_SUPPORT_COST and LOST_INTERCHANGE</t>
+  </si>
+  <si>
+    <t>These columns are returning negative and positive values. They should all be negative since they are costs. When there is no fraud and the ML model does not catch fraud (TRUE NEGATIVE), the amount should be 0 in all these columns.</t>
+  </si>
+  <si>
+    <t>Joined with the TRANSACTIONS and FRAUD_DECISIONS table and determined that all negative values are from TRUE NEGATIVE results. Returned 0 in all these columns the it is a TRUE POSITIVE, and the other values were changed from positive to negative since they should be represented as debits.</t>
   </si>
 </sst>
 </file>
@@ -349,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -381,11 +468,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="60">
     <dxf>
       <font>
         <strike val="0"/>
@@ -571,6 +661,639 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1033,42 +1756,84 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05C0FE4D-3D83-48C0-8912-23AD1347B2CD}" name="CURRENCY_EXCHANGE_RATES_LOG" displayName="CURRENCY_EXCHANGE_RATES_LOG" ref="A1:E2" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05C0FE4D-3D83-48C0-8912-23AD1347B2CD}" name="CURRENCY_EXCHANGE_RATES_LOG" displayName="CURRENCY_EXCHANGE_RATES_LOG" ref="A1:E2" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A1:E2" xr:uid="{05C0FE4D-3D83-48C0-8912-23AD1347B2CD}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2E40A0B3-AF90-4182-9843-2288801456DE}" name="COLUMN" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{F80B9787-EB7F-4E48-848A-5C6AA8F617DA}" name="ISSUE" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{0AB4CDCB-C236-4A3C-A4A4-9D44F21813D8}" name="ROW_COUNT" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{54E6A82B-991C-4065-96DF-727003752F56}" name="SOLVABLE?" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{7862C159-CC1E-4693-A947-D23804304F60}" name="RESOLUTION" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{2E40A0B3-AF90-4182-9843-2288801456DE}" name="COLUMN" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{F80B9787-EB7F-4E48-848A-5C6AA8F617DA}" name="ISSUE" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{0AB4CDCB-C236-4A3C-A4A4-9D44F21813D8}" name="ROW_COUNT" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{54E6A82B-991C-4065-96DF-727003752F56}" name="SOLVABLE?" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{7862C159-CC1E-4693-A947-D23804304F60}" name="RESOLUTION" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}" name="ACCOUNTS_LOG" displayName="ACCOUNTS_LOG" ref="A1:E9" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}" name="ACCOUNTS_LOG" displayName="ACCOUNTS_LOG" ref="A1:E9" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A1:E9" xr:uid="{2559DFCC-38D7-4B21-B9B4-4C2119AFCC1B}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24C76CF5-60AC-4D99-B257-103FA77CA877}" name="COLUMN" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{3337A670-71E0-4223-B5A5-44BCF535FADF}" name="ISSUE" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{75E5D8EA-C827-466C-A54E-C6D233FF37A9}" name="ROW_COUNT" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{E754BFA5-49D4-4DE6-974C-68E66960C0FB}" name="SOLVABLE?" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{E655503B-E1BA-4C6B-855C-199DC3D0C0C1}" name="RESOLUTION" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{24C76CF5-60AC-4D99-B257-103FA77CA877}" name="COLUMN" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{3337A670-71E0-4223-B5A5-44BCF535FADF}" name="ISSUE" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{75E5D8EA-C827-466C-A54E-C6D233FF37A9}" name="ROW_COUNT" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{E754BFA5-49D4-4DE6-974C-68E66960C0FB}" name="SOLVABLE?" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{E655503B-E1BA-4C6B-855C-199DC3D0C0C1}" name="RESOLUTION" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80E774B3-ED81-44B3-B55B-CB30FBB2CC6A}" name="CUSTOMERS_LOG" displayName="CUSTOMERS_LOG" ref="A1:E7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80E774B3-ED81-44B3-B55B-CB30FBB2CC6A}" name="CUSTOMERS_LOG" displayName="CUSTOMERS_LOG" ref="A1:E7" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="A1:E7" xr:uid="{80E774B3-ED81-44B3-B55B-CB30FBB2CC6A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{61E96C8D-2220-4567-BB54-92EC049CF4F5}" name="COLUMN" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D071CD65-CD39-4278-9D0A-DFB78B630E35}" name="ISSUE" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{83A03F84-5429-40D2-9146-4D040C3B0952}" name="ROW_COUNT" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{9E8CE933-1F0D-4B77-B634-8E01CE3B889D}" name="SOLVABLE?" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{FA4FB0EF-2A46-4B38-9DA8-CA7E9F384D25}" name="RESOLUTION" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{61E96C8D-2220-4567-BB54-92EC049CF4F5}" name="COLUMN" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{D071CD65-CD39-4278-9D0A-DFB78B630E35}" name="ISSUE" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{83A03F84-5429-40D2-9146-4D040C3B0952}" name="ROW_COUNT" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{9E8CE933-1F0D-4B77-B634-8E01CE3B889D}" name="SOLVABLE?" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{FA4FB0EF-2A46-4B38-9DA8-CA7E9F384D25}" name="RESOLUTION" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DFF76B32-0D88-4103-915F-6B62B1B4AFFF}" name="FRAUD_DECISIONS_LOG" displayName="FRAUD_DECISIONS_LOG" ref="A1:E4" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
+  <autoFilter ref="A1:E4" xr:uid="{DFF76B32-0D88-4103-915F-6B62B1B4AFFF}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{58E14777-AB82-43DC-89AC-E9CEDBDD51C2}" name="COLUMN" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{CD5DC19E-3845-4329-AEBC-C3A33F3DCEB3}" name="ISSUE" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{7C347363-31AE-4A2F-B324-B50D6900D2C2}" name="ROW_COUNT" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{C5B0C625-5DA5-4F0F-B3EA-75D8A4417CC9}" name="SOLVABLE?" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{29A5587B-A438-4F7D-9060-D89A0DC9DBA9}" name="RESOLUTION" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9AFE3C75-C06E-4CDD-9EC4-5D3937D01F5A}" name="TRANSACTIONS_LOG" displayName="TRANSACTIONS_LOG" ref="A1:E6" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:E6" xr:uid="{9AFE3C75-C06E-4CDD-9EC4-5D3937D01F5A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1F611AEE-665A-48CE-A0D0-B23C83D04AEB}" name="COLUMN" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{B281A476-9E4C-4D0C-9A1C-03B774227A46}" name="ISSUE" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{6759004E-A61B-4380-9379-9C271874DBA3}" name="ROW_COUNT" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{47FCE10C-909B-40AA-9C22-CB2B59DB8A2D}" name="SOLVABLE?" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{F197FA95-C4C9-4E19-9D71-6B25B6A40731}" name="RESOLUTION" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6D850D2E-A420-46EC-963D-C048357A38A4}" name="FRAUD_COSTS_LOG" displayName="FRAUD_COSTS_LOG" ref="A1:E2" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E2" xr:uid="{6D850D2E-A420-46EC-963D-C048357A38A4}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7EC1EFB9-4D04-4CCC-852C-98A4C4AAF1E1}" name="COLUMN" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{346ABBF4-9F6E-4173-8596-D73DD5C40A0C}" name="ISSUE" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{748912C1-766A-4D0E-AEF4-9851D3B5F711}" name="ROW_COUNT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{03A6C765-E8DC-49D4-9C83-40DC97B0EB10}" name="SOLVABLE?" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E2841513-C325-4793-9E02-2AAE68390DA4}" name="RESOLUTION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1754,4 +2519,268 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583C1207-263E-441F-96F3-023CC51611A0}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="89.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="7">
+        <v>26395</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB2C2A0-E7B9-4447-A586-29DF92C5451C}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="103.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="294" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="84" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2325</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A8AFBC-4185-47DE-95E6-051A8A308265}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="2" max="2" width="60.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="126" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="7">
+        <v>47424</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>